--- a/AAII_Financials/Yearly/TRN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRN_YR_FIN.xlsx
@@ -2267,10 +2267,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>416600</v>
+        <v>405700</v>
       </c>
       <c r="E43" s="3">
-        <v>381500</v>
+        <v>371900</v>
       </c>
       <c r="F43" s="3">
         <v>368700</v>
